--- a/main/ig/StructureDefinition-fr-lm-encounter.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T15:39:37+00:00</t>
+    <t>2026-08-05T12:15:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-encounter.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:15:23+00:00</t>
+    <t>2026-08-11T08:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-encounter.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T08:03:55+00:00</t>
+    <t>2026-08-11T09:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-encounter.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T09:29:09+00:00</t>
+    <t>2026-08-13T09:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-encounter.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:45:33+00:00</t>
+    <t>2026-08-13T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-encounter.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:36:19+00:00</t>
+    <t>2026-08-14T12:00:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-encounter.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:00:06+00:00</t>
+    <t>2026-08-14T14:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-encounter.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-encounter.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1251" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1251" uniqueCount="193">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T14:57:39+00:00</t>
+    <t>2026-08-20T08:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -531,6 +531,9 @@
   </si>
   <si>
     <t>Modalité d'entrée d'un patient en ES (urgence, programmée, etc...).</t>
+  </si>
+  <si>
+    <t>required</t>
   </si>
   <si>
     <t>jdv-modalite-entree : Modalité d'entrée en établissement de santé</t>
@@ -3922,13 +3925,13 @@
         <v>73</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>73</v>
+        <v>167</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>73</v>
@@ -3963,10 +3966,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -3989,13 +3992,13 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4046,7 +4049,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4063,10 +4066,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4092,10 +4095,10 @@
         <v>80</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4146,7 +4149,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
@@ -4163,10 +4166,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4192,10 +4195,10 @@
         <v>132</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4222,10 +4225,10 @@
         <v>73</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>73</v>
+        <v>167</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Z33" t="s" s="2">
         <v>73</v>
@@ -4246,7 +4249,7 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
@@ -4263,10 +4266,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4289,13 +4292,13 @@
         <v>73</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4346,7 +4349,7 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>74</v>
@@ -4363,10 +4366,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4392,10 +4395,10 @@
         <v>80</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4446,7 +4449,7 @@
         <v>73</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>74</v>
@@ -4463,10 +4466,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4492,10 +4495,10 @@
         <v>145</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4546,7 +4549,7 @@
         <v>73</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>74</v>
@@ -4563,10 +4566,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4589,13 +4592,13 @@
         <v>73</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4646,7 +4649,7 @@
         <v>73</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -4663,10 +4666,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4689,13 +4692,13 @@
         <v>73</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -4746,7 +4749,7 @@
         <v>73</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>74</v>
@@ -4763,10 +4766,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -4789,13 +4792,13 @@
         <v>73</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -4846,7 +4849,7 @@
         <v>73</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>74</v>
